--- a/api/templates/devices_and_sites_overview/uk.xlsx
+++ b/api/templates/devices_and_sites_overview/uk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\devices_and_sites_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A402B3-D068-4488-AD86-06CF8BFDD093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CF6F97-FF71-42AF-81D3-129782273D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>Примітки: цей звіт містить лише ті витратні матеріали, які колись відстежувалися на сайтах</t>
+  </si>
+  <si>
+    <t>Є в наявності, але закінчився термін придатності</t>
+  </si>
+  <si>
+    <t>&lt;quantityExpired&gt;</t>
   </si>
 </sst>
 </file>
@@ -743,9 +749,12 @@
         <v>17</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -766,9 +775,12 @@
         <v>6</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="O9" s="1"/>

--- a/api/templates/devices_and_sites_overview/uk.xlsx
+++ b/api/templates/devices_and_sites_overview/uk.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\devices_and_sites_overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\devices_and_sites_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B386E67-0BE2-4FD4-B85E-73745885E68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129DC48E-45E3-4032-A5F9-7F85B20BBB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneXpert Devices" sheetId="1" r:id="rId1"/>
@@ -498,25 +498,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -554,16 +542,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -948,206 +952,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T12"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
-    <col min="5" max="5" width="22.796875" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="5" max="5" width="22.75" customWidth="1"/>
     <col min="6" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14.69921875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14.3984375" style="8" customWidth="1"/>
-    <col min="12" max="14" width="14.3984375" style="7" customWidth="1"/>
-    <col min="15" max="15" width="13.19921875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="10.5" style="7" customWidth="1"/>
-    <col min="17" max="17" width="18.296875" style="7" customWidth="1"/>
-    <col min="18" max="18" width="11" style="8" customWidth="1"/>
+    <col min="10" max="10" width="14.75" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.375" style="4" customWidth="1"/>
+    <col min="12" max="14" width="14.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.25" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.5" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.25" style="3" customWidth="1"/>
+    <col min="18" max="18" width="11" style="4" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="1015" max="1024" width="9.296875" customWidth="1"/>
+    <col min="1015" max="1024" width="9.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="20" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:20" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:20" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" spans="1:20" s="14" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="N9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="P9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="Q9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="R9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S9" s="12" t="s">
+      <c r="S9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="12" t="s">
+      <c r="T9" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="18" t="s">
+      <c r="O10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="18" t="s">
+      <c r="P10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" s="18" t="s">
+      <c r="Q10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="R10" s="19" t="s">
+      <c r="R10" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="S10" s="15" t="s">
+      <c r="S10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="T10" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1166,116 +1170,116 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.796875" customWidth="1"/>
-    <col min="2" max="2" width="17.3984375" customWidth="1"/>
-    <col min="3" max="3" width="21.09765625" customWidth="1"/>
-    <col min="4" max="4" width="27.19921875" customWidth="1"/>
-    <col min="5" max="5" width="16.09765625" customWidth="1"/>
-    <col min="6" max="6" width="25.69921875" customWidth="1"/>
-    <col min="7" max="7" width="13.796875" customWidth="1"/>
-    <col min="8" max="8" width="15.69921875" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="7"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="11" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1291,142 +1295,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.09765625" customWidth="1"/>
-    <col min="2" max="9" width="8.796875" style="7" customWidth="1"/>
-    <col min="10" max="10" width="12.296875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="14.296875" style="7" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="7" customWidth="1"/>
+    <col min="1" max="1" width="33.125" customWidth="1"/>
+    <col min="2" max="9" width="8.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="1" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="25" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="24">
+    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23"/>
+      <c r="B9" s="1">
         <v>5011</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="1">
         <v>5007</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="1">
         <v>5006</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="1">
         <v>2008</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="1">
         <v>2005</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="1">
         <v>2037</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="1">
         <v>2025</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="1">
         <v>2022</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="7" t="e">
+      <c r="L10" s="3" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
@@ -1446,307 +1450,307 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.09765625" customWidth="1"/>
-    <col min="2" max="2" width="39.19921875" customWidth="1"/>
-    <col min="3" max="3" width="100.59765625" customWidth="1"/>
+    <col min="1" max="1" width="5.125" customWidth="1"/>
+    <col min="2" max="2" width="39.25" customWidth="1"/>
+    <col min="3" max="3" width="100.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25">
+    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
         <v>1001</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>1002</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
         <v>1004</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>1005</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="19" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>1006</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>1007</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>1017</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>1018</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
         <v>2003</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
+    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
         <v>2005</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
         <v>2008</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
         <v>2009</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
+    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>2011</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25">
+    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
         <v>2014</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25">
+    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
         <v>2016</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>2018</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>2022</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25">
+    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>2025</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25">
+    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>2032</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25">
+    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
         <v>2034</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="19" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25">
+    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19">
         <v>2037</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25">
+    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19">
         <v>4010</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25">
+    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19">
         <v>4017</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="19" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25">
+    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19">
         <v>5006</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="19" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25">
+    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19">
         <v>5007</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25">
+    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19">
         <v>5011</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="19" t="s">
         <v>112</v>
       </c>
     </row>

--- a/api/templates/devices_and_sites_overview/uk.xlsx
+++ b/api/templates/devices_and_sites_overview/uk.xlsx
@@ -1,34 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\devices_and_sites_overview\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gianatiempo/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129DC48E-45E3-4032-A5F9-7F85B20BBB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6310DE7-174F-DC4E-8CF6-19D61FE43219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3320" yWindow="1120" windowWidth="28800" windowHeight="16440" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GeneXpert Devices" sheetId="1" r:id="rId1"/>
-    <sheet name="GeneXpert Inventory by Site" sheetId="2" r:id="rId2"/>
-    <sheet name="GeneXpert Errors by Devices" sheetId="3" r:id="rId3"/>
+    <sheet name="Xpert Site Summary Report" sheetId="1" r:id="rId1"/>
+    <sheet name="Xpert Site Inventory" sheetId="2" r:id="rId2"/>
+    <sheet name="Xpert Site Errors by Devices" sheetId="3" r:id="rId3"/>
     <sheet name="Error Codes" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -41,9 +37,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="114">
   <si>
-    <t>Пристрої GeneXpert</t>
-  </si>
-  <si>
     <t>Дати: &lt;Dates&gt;</t>
   </si>
   <si>
@@ -182,9 +175,6 @@
     <t>&lt;totalOtherTests&gt;</t>
   </si>
   <si>
-    <t>Інвентаризація GeneXpert за сайтом</t>
-  </si>
-  <si>
     <t>Примітки: цей звіт містить лише ті витратні матеріали, які колись відстежувалися на сайтах</t>
   </si>
   <si>
@@ -236,9 +226,6 @@
     <t>&lt;projectedWaste&gt;</t>
   </si>
   <si>
-    <t>Помилки GeneXpert за пристроями</t>
-  </si>
-  <si>
     <t>Тип помилки</t>
   </si>
   <si>
@@ -381,6 +368,15 @@
   </si>
   <si>
     <t>Оновлення останнього результату</t>
+  </si>
+  <si>
+    <t>Пристрої Xpert</t>
+  </si>
+  <si>
+    <t>Інвентаризація Xpert за сайтом</t>
+  </si>
+  <si>
+    <t>Помилки Xpert за пристроями</t>
   </si>
 </sst>
 </file>
@@ -547,27 +543,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,201 +948,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T12"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="5" max="5" width="22.75" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
     <col min="6" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14.75" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="4" customWidth="1"/>
-    <col min="12" max="14" width="14.375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="4" customWidth="1"/>
+    <col min="12" max="14" width="14.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="3" customWidth="1"/>
     <col min="16" max="16" width="10.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="18.25" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="3" customWidth="1"/>
     <col min="18" max="18" width="11" style="4" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="1015" max="1024" width="9.25" customWidth="1"/>
+    <col min="1015" max="1024" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="20" t="s">
+    </row>
+    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="1:20" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="20"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:20" ht="132.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="22"/>
+    </row>
+    <row r="8" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>6</v>
-      </c>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:20" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="20"/>
-    </row>
-    <row r="8" spans="1:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="R9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="9" t="s">
+      <c r="S9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="T9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="8" t="s">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="B10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="G10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="26" t="s">
+      <c r="J10" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="K10" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="L10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="M10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="N10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="O10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="O10" s="14" t="s">
+      <c r="P10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="Q10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="R10" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="R10" s="15" t="s">
+      <c r="S10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="S10" s="11" t="s">
+      <c r="T10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="T10" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1170,117 +1166,117 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="H9" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1295,77 +1291,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.125" customWidth="1"/>
-    <col min="2" max="9" width="8.75" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.25" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="9" width="8.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" style="3" customWidth="1"/>
     <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>7</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="25"/>
       <c r="B9" s="1">
         <v>5011</v>
       </c>
@@ -1391,44 +1387,44 @@
         <v>2022</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="L10" s="3" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
@@ -1450,308 +1446,308 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="39.25" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>1001</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
         <v>1002</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
         <v>1004</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
         <v>1005</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1006</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
         <v>1007</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
         <v>1017</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
         <v>1018</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
         <v>2003</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
         <v>2005</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
         <v>2008</v>
       </c>
       <c r="B12" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
         <v>2009</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
         <v>2011</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
         <v>2014</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
         <v>2016</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
         <v>2018</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
         <v>2022</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
         <v>2025</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
         <v>2032</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
         <v>2034</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
         <v>2037</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
         <v>4010</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
         <v>4017</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>5006</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
         <v>5007</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
         <v>5011</v>
       </c>
       <c r="B27" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
